--- a/static/example_sheets/Field sampling (external).xlsx
+++ b/static/example_sheets/Field sampling (external).xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\glj523\Documents\github repoes\upload_web_app\static\example_sheets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\magnu\Documents\Git Repoes\gg-metadatabase-ui\static\example_sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BDACDFD-706D-40F0-BEB7-97766559696A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41D4F50C-97F5-4334-BB90-7698B594515F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{F20BE04D-14A6-4DFA-9322-DA461E992517}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{F20BE04D-14A6-4DFA-9322-DA461E992517}"/>
   </bookViews>
   <sheets>
     <sheet name="eDNA_Archive_sampling_(20231027" sheetId="2" r:id="rId1"/>
@@ -46,9 +46,9 @@
   <commentList>
     <comment ref="P1" authorId="0" shapeId="0" xr:uid="{6FC7414E-1184-43F7-9F14-90F3FC65C183}">
       <text>
-        <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t xml:space="preserve">[Trådet kommentar]
+Din version af Excel lader dig læse denne trådede kommentar. Eventuelle ændringer vil dog blive fjernet, hvis filen åbnes i en nyere version af Excel. Få mere at vide: https://go.microsoft.com/fwlink/?linkid=870924
+Kommentar:
     URI: MIXS:0000018 </t>
       </text>
     </comment>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="121">
   <si>
     <t>Expected column names and positions:</t>
   </si>
@@ -172,18 +172,6 @@
     <t>Sample label (sticker)</t>
   </si>
   <si>
-    <t>jkl223_hollerup_20230914_1</t>
-  </si>
-  <si>
-    <t>jkl223_hollerup_20230914_2</t>
-  </si>
-  <si>
-    <t>jkl223_hollerup_20230914_3</t>
-  </si>
-  <si>
-    <t>&lt;ku-id&gt;_&lt;sampling_site&gt;_&lt;sampling_date&gt;_&lt;no&gt;</t>
-  </si>
-  <si>
     <t xml:space="preserve">Latitude </t>
   </si>
   <si>
@@ -223,15 +211,6 @@
     <t>CGG_3_000002</t>
   </si>
   <si>
-    <t>(10, 50)</t>
-  </si>
-  <si>
-    <t>[10, 20]</t>
-  </si>
-  <si>
-    <t>(-10, -5]</t>
-  </si>
-  <si>
     <t>Lacustrine</t>
   </si>
   <si>
@@ -355,9 +334,6 @@
     <t xml:space="preserve">If working half and archive half are stored different places, report two locations seperated by semi-colon and preceded by either A: or W: </t>
   </si>
   <si>
-    <t>A standardized unique ID for the physical label. Consist of ku ID of field trip representative/leader/PI + sampling site (as local as possible) + collection date + incrementing integer.</t>
-  </si>
-  <si>
     <t>A: shelf 4.5; W: shelf 4.6</t>
   </si>
   <si>
@@ -385,12 +361,6 @@
     <t>Point from where the depth measurement was taken</t>
   </si>
   <si>
-    <t>Hollerup</t>
-  </si>
-  <si>
-    <t>Denmark</t>
-  </si>
-  <si>
     <t>Referencing this google sheet: https://docs.google.com/spreadsheets/d/10TWDtKMug4yzOQUP7Q4APIoPNHQXCFX_RasijIgyCAA/edit?usp=sharing</t>
   </si>
   <si>
@@ -418,12 +388,6 @@
     <t>[1, 105)</t>
   </si>
   <si>
-    <t>(1, 105)</t>
-  </si>
-  <si>
-    <t>[1, 105]</t>
-  </si>
-  <si>
     <t>Sample provider(s) (external)</t>
   </si>
   <si>
@@ -434,6 +398,36 @@
   </si>
   <si>
     <t xml:space="preserve">Email </t>
+  </si>
+  <si>
+    <t>x_&lt;last name of external provider&gt;_&lt;sampling_site&gt;_&lt;sampling_date&gt;_&lt;no&gt;</t>
+  </si>
+  <si>
+    <t>A standardized unique ID for the physical label. Consist of an x (for external) + last name of external provider + sampling site (as local as possible) + collection date + incrementing integer.</t>
+  </si>
+  <si>
+    <t>x_jensen_greenland_20230914_1</t>
+  </si>
+  <si>
+    <t>x_jensen_greenland_20230914_2</t>
+  </si>
+  <si>
+    <t>x_jensen_greenland_20230914_3</t>
+  </si>
+  <si>
+    <t>Greenland</t>
+  </si>
+  <si>
+    <t>Remote Rural Area</t>
+  </si>
+  <si>
+    <t>[10, 50)</t>
+  </si>
+  <si>
+    <t>[10, 20)</t>
+  </si>
+  <si>
+    <t>[-10, -5)</t>
   </si>
 </sst>
 </file>
@@ -663,10 +657,10 @@
     </xf>
   </cellXfs>
   <cellStyles count="8">
-    <cellStyle name="Check Cell" xfId="6" builtinId="23"/>
     <cellStyle name="Comma 2" xfId="3" xr:uid="{8942F21F-F0D4-468F-A2D9-2DD07A9F09D0}"/>
     <cellStyle name="Explanatory Text 2" xfId="2" xr:uid="{EEC8BC1F-FCCB-4C2D-96AE-E4673B111AFF}"/>
-    <cellStyle name="Hyperlink" xfId="7" builtinId="8"/>
+    <cellStyle name="Kontrollér celle" xfId="6" builtinId="23"/>
+    <cellStyle name="Link" xfId="7" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{C43A14CE-CD9A-4CDB-8396-19B2B1DC1FD5}"/>
     <cellStyle name="Normal 4" xfId="4" xr:uid="{1133FEEC-7998-4312-B355-8FD805FAFB7D}"/>
@@ -692,9 +686,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022 Tema">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -732,7 +726,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -838,7 +832,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -980,7 +974,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1006,11 +1000,11 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="34" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.77734375" customWidth="1"/>
+    <col min="2" max="2" width="35.21875" customWidth="1"/>
     <col min="3" max="3" width="8.21875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.88671875" customWidth="1"/>
+    <col min="6" max="6" width="20.44140625" customWidth="1"/>
     <col min="7" max="7" width="22" customWidth="1"/>
     <col min="8" max="8" width="21.21875" customWidth="1"/>
     <col min="9" max="9" width="13.21875" bestFit="1" customWidth="1"/>
@@ -1069,28 +1063,28 @@
         <v>15</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>16</v>
@@ -1099,25 +1093,25 @@
         <v>17</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="O1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="P1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="R1" s="3" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>19</v>
@@ -1141,7 +1135,7 @@
         <v>27</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AC1" s="1" t="s">
         <v>28</v>
@@ -1173,16 +1167,13 @@
         <v>9</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>35</v>
+        <v>113</v>
       </c>
       <c r="D2" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="E2" s="18" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="F2" s="18" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="G2" s="19">
         <v>61.139899999999997</v>
@@ -1191,27 +1182,27 @@
         <v>-45.534700000000001</v>
       </c>
       <c r="I2" s="18" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="J2"/>
       <c r="K2"/>
       <c r="L2" s="18" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="M2" s="18" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="N2" s="18" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="O2" s="18">
         <v>10</v>
       </c>
       <c r="P2" s="18" t="s">
-        <v>52</v>
+        <v>118</v>
       </c>
       <c r="Q2" s="18" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="R2" s="18">
         <v>10</v>
@@ -1223,58 +1214,55 @@
         <v>4</v>
       </c>
       <c r="U2" s="18" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="V2" s="19" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="W2" s="18" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="X2" s="18" t="s">
         <v>5</v>
       </c>
       <c r="Y2" s="18" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="Z2" s="18">
         <v>37</v>
       </c>
       <c r="AA2" s="18" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="AB2" s="18" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="AC2" s="18" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="AD2" s="18" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="AE2" s="18" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="AF2" s="18" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="AG2" s="18" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:36" s="18" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="18" t="s">
-        <v>36</v>
+        <v>114</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="E3" s="18" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="F3" s="18" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="G3" s="19">
         <v>61.139899999999997</v>
@@ -1283,27 +1271,27 @@
         <v>-45.534700000000001</v>
       </c>
       <c r="I3" s="18" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="J3"/>
       <c r="K3"/>
       <c r="L3" s="18" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="M3" s="18" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="N3" s="18" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="O3" s="18">
         <v>200</v>
       </c>
       <c r="P3" s="18" t="s">
-        <v>53</v>
+        <v>119</v>
       </c>
       <c r="Q3" s="18" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="R3" s="18">
         <v>200</v>
@@ -1312,61 +1300,58 @@
         <v>200</v>
       </c>
       <c r="T3" s="18" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="U3" s="18" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="V3" s="19" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="W3" s="18" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="X3" s="18" t="s">
         <v>5</v>
       </c>
       <c r="Y3" s="18" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="Z3" s="18">
         <v>37</v>
       </c>
       <c r="AA3" s="18" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="AB3" s="18" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="AC3" s="18" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="AD3" s="18" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="AE3" s="18" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="AF3" s="18" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="AG3" s="18" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:36" s="18" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
       <c r="B4" s="18" t="s">
-        <v>37</v>
+        <v>115</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="E4" s="18" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="F4" s="18" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="G4" s="19">
         <v>61.139899999999997</v>
@@ -1375,75 +1360,75 @@
         <v>-45.534700000000001</v>
       </c>
       <c r="I4" s="18" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="J4"/>
       <c r="K4"/>
       <c r="L4" s="18" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="M4" s="18" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="N4" s="18" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="O4" s="18" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="P4" s="18" t="s">
-        <v>54</v>
+        <v>120</v>
       </c>
       <c r="Q4" s="18" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="R4" s="18" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="S4" s="18" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="T4" s="18" t="s">
         <v>6</v>
       </c>
       <c r="U4" s="18" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="V4" s="19" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="W4" s="18" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="X4" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y4" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="Z4" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="AA4" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB4" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="AC4" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="AD4" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="AE4" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="AF4" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="Y4" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="Z4" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="AA4" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="AB4" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="AC4" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="AD4" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="AE4" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="AF4" s="18" t="s">
-        <v>84</v>
-      </c>
       <c r="AG4" s="18" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.3">
@@ -1455,17 +1440,17 @@
         <v>2</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>7</v>
@@ -1474,45 +1459,45 @@
         <v>8</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="J6"/>
       <c r="K6"/>
       <c r="L6" s="5" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="N6" s="5" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="P6" s="5" t="s">
         <v>11</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="S6" s="5" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="T6" s="5" t="s">
         <v>11</v>
       </c>
       <c r="U6" s="5" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="V6" s="5" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="W6" s="5" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="X6" s="5" t="s">
         <v>14</v>
@@ -1521,37 +1506,37 @@
         <v>13</v>
       </c>
       <c r="Z6" s="5" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="AA6" s="5" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="AB6" s="5" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="AC6" s="5" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="AD6" s="5" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="AE6" s="5" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="AF6" s="5" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AG6" s="5" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AH6" s="5" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="AI6" s="5" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="AJ6" s="5" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:36" s="5" customFormat="1" ht="61.2" x14ac:dyDescent="0.3">
@@ -1559,84 +1544,84 @@
         <v>12</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
       <c r="G7" s="9" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="H7" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="N7" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="O7" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="P7" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q7" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="R7" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="S7" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="T7" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="I7" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="L7" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="M7" s="10" t="s">
+      <c r="V7" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y7" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z7" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="AA7" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC7" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="AD7" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE7" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AF7" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="N7" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="O7" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="P7" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q7" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="R7" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="S7" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="T7" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="V7" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y7" s="5" t="s">
+      <c r="AG7" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="Z7" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="AA7" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="AC7" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="AD7" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="AE7" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="AF7" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="AG7" s="5" t="s">
-        <v>85</v>
-      </c>
       <c r="AH7" s="5" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="AI7" s="5" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:36" s="6" customFormat="1" x14ac:dyDescent="0.2">

--- a/static/example_sheets/Field sampling (external).xlsx
+++ b/static/example_sheets/Field sampling (external).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\magnu\Documents\Git Repoes\gg-metadatabase-ui\static\example_sheets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\glj523\Documents\github repoes\upload_web_app\static\example_sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41D4F50C-97F5-4334-BB90-7698B594515F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B21BAA7-38BE-45AE-B4F4-19EB53181015}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{F20BE04D-14A6-4DFA-9322-DA461E992517}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{F20BE04D-14A6-4DFA-9322-DA461E992517}"/>
   </bookViews>
   <sheets>
     <sheet name="eDNA_Archive_sampling_(20231027" sheetId="2" r:id="rId1"/>
@@ -46,9 +46,9 @@
   <commentList>
     <comment ref="P1" authorId="0" shapeId="0" xr:uid="{6FC7414E-1184-43F7-9F14-90F3FC65C183}">
       <text>
-        <t xml:space="preserve">[Trådet kommentar]
-Din version af Excel lader dig læse denne trådede kommentar. Eventuelle ændringer vil dog blive fjernet, hvis filen åbnes i en nyere version af Excel. Få mere at vide: https://go.microsoft.com/fwlink/?linkid=870924
-Kommentar:
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     URI: MIXS:0000018 </t>
       </text>
     </comment>
@@ -388,18 +388,6 @@
     <t>[1, 105)</t>
   </si>
   <si>
-    <t>Sample provider(s) (external)</t>
-  </si>
-  <si>
-    <t>Sample provider(s) email (external)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Full name of external provider </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Email </t>
-  </si>
-  <si>
     <t>x_&lt;last name of external provider&gt;_&lt;sampling_site&gt;_&lt;sampling_date&gt;_&lt;no&gt;</t>
   </si>
   <si>
@@ -428,6 +416,18 @@
   </si>
   <si>
     <t>[-10, -5)</t>
+  </si>
+  <si>
+    <t>External sample provider(s) name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">External sample provider(s) email </t>
+  </si>
+  <si>
+    <t>Full name of external provider. If multiple: seperate by semi colon.</t>
+  </si>
+  <si>
+    <t>Email of external sample provider. If multiple: Seperate by semi colon.</t>
   </si>
 </sst>
 </file>
@@ -657,10 +657,10 @@
     </xf>
   </cellXfs>
   <cellStyles count="8">
+    <cellStyle name="Check Cell" xfId="6" builtinId="23"/>
     <cellStyle name="Comma 2" xfId="3" xr:uid="{8942F21F-F0D4-468F-A2D9-2DD07A9F09D0}"/>
     <cellStyle name="Explanatory Text 2" xfId="2" xr:uid="{EEC8BC1F-FCCB-4C2D-96AE-E4673B111AFF}"/>
-    <cellStyle name="Kontrollér celle" xfId="6" builtinId="23"/>
-    <cellStyle name="Link" xfId="7" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="7" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{C43A14CE-CD9A-4CDB-8396-19B2B1DC1FD5}"/>
     <cellStyle name="Normal 4" xfId="4" xr:uid="{1133FEEC-7998-4312-B355-8FD805FAFB7D}"/>
@@ -686,9 +686,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022 Tema">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -726,7 +726,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -832,7 +832,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -974,7 +974,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1008,8 +1008,8 @@
     <col min="7" max="7" width="22" customWidth="1"/>
     <col min="8" max="8" width="21.21875" customWidth="1"/>
     <col min="9" max="9" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.21875" customWidth="1"/>
-    <col min="11" max="11" width="14.88671875" customWidth="1"/>
+    <col min="10" max="10" width="17.44140625" customWidth="1"/>
+    <col min="11" max="11" width="19.77734375" customWidth="1"/>
     <col min="12" max="12" width="11" customWidth="1"/>
     <col min="13" max="13" width="8.88671875" customWidth="1"/>
     <col min="14" max="14" width="29.77734375" customWidth="1"/>
@@ -1081,10 +1081,10 @@
         <v>95</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>16</v>
@@ -1167,13 +1167,13 @@
         <v>9</v>
       </c>
       <c r="B2" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2" s="18" t="s">
         <v>113</v>
-      </c>
-      <c r="D2" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="F2" s="18" t="s">
-        <v>117</v>
       </c>
       <c r="G2" s="19">
         <v>61.139899999999997</v>
@@ -1199,7 +1199,7 @@
         <v>10</v>
       </c>
       <c r="P2" s="18" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="Q2" s="18" t="s">
         <v>45</v>
@@ -1256,13 +1256,13 @@
     <row r="3" spans="1:36" s="18" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="18" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F3" s="18" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="G3" s="19">
         <v>61.139899999999997</v>
@@ -1288,7 +1288,7 @@
         <v>200</v>
       </c>
       <c r="P3" s="18" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="Q3" s="18" t="s">
         <v>46</v>
@@ -1345,13 +1345,13 @@
     <row r="4" spans="1:36" s="18" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
       <c r="B4" s="18" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F4" s="18" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="G4" s="19">
         <v>61.139899999999997</v>
@@ -1377,7 +1377,7 @@
         <v>105</v>
       </c>
       <c r="P4" s="18" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="Q4" s="18" t="s">
         <v>47</v>
@@ -1440,7 +1440,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5" t="s">
@@ -1544,7 +1544,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
@@ -1558,10 +1558,10 @@
         <v>96</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="L7" s="5" t="s">
         <v>67</v>

--- a/static/example_sheets/Field sampling (external).xlsx
+++ b/static/example_sheets/Field sampling (external).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\glj523\Documents\github repoes\upload_web_app\static\example_sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B21BAA7-38BE-45AE-B4F4-19EB53181015}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E1E9522-0E99-4F1F-A633-F8FDB22D2E1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{F20BE04D-14A6-4DFA-9322-DA461E992517}"/>
+    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{F20BE04D-14A6-4DFA-9322-DA461E992517}"/>
   </bookViews>
   <sheets>
     <sheet name="eDNA_Archive_sampling_(20231027" sheetId="2" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="125">
   <si>
     <t>Expected column names and positions:</t>
   </si>
@@ -406,9 +406,6 @@
     <t>Greenland</t>
   </si>
   <si>
-    <t>Remote Rural Area</t>
-  </si>
-  <si>
     <t>[10, 50)</t>
   </si>
   <si>
@@ -428,6 +425,23 @@
   </si>
   <si>
     <t>Email of external sample provider. If multiple: Seperate by semi colon.</t>
+  </si>
+  <si>
+    <t>An id for the physical QR code on the sample</t>
+  </si>
+  <si>
+    <t>If relevant. Otherwise leave blank.</t>
+  </si>
+  <si>
+    <t>???</t>
+  </si>
+  <si>
+    <t>Eg. Glacial, Lacustrine
+Fluvial, Aeolian,Peat
+Soil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Specify the storage setting </t>
   </si>
 </sst>
 </file>
@@ -1081,10 +1095,10 @@
         <v>95</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>118</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>16</v>
@@ -1172,9 +1186,6 @@
       <c r="D2" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="F2" s="18" t="s">
-        <v>113</v>
-      </c>
       <c r="G2" s="19">
         <v>61.139899999999997</v>
       </c>
@@ -1199,7 +1210,7 @@
         <v>10</v>
       </c>
       <c r="P2" s="18" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q2" s="18" t="s">
         <v>45</v>
@@ -1261,9 +1272,6 @@
       <c r="D3" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="F3" s="18" t="s">
-        <v>113</v>
-      </c>
       <c r="G3" s="19">
         <v>61.139899999999997</v>
       </c>
@@ -1288,7 +1296,7 @@
         <v>200</v>
       </c>
       <c r="P3" s="18" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="Q3" s="18" t="s">
         <v>46</v>
@@ -1350,9 +1358,6 @@
       <c r="D4" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="F4" s="18" t="s">
-        <v>113</v>
-      </c>
       <c r="G4" s="19">
         <v>61.139899999999997</v>
       </c>
@@ -1377,7 +1382,7 @@
         <v>105</v>
       </c>
       <c r="P4" s="18" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q4" s="18" t="s">
         <v>47</v>
@@ -1442,7 +1447,9 @@
       <c r="B6" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="C6" s="5"/>
+      <c r="C6" s="5" t="s">
+        <v>122</v>
+      </c>
       <c r="D6" s="5" t="s">
         <v>64</v>
       </c>
@@ -1461,8 +1468,12 @@
       <c r="I6" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="J6"/>
-      <c r="K6"/>
+      <c r="J6" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>64</v>
+      </c>
       <c r="L6" s="5" t="s">
         <v>66</v>
       </c>
@@ -1546,8 +1557,16 @@
       <c r="B7" s="5" t="s">
         <v>108</v>
       </c>
+      <c r="C7" s="5" t="s">
+        <v>120</v>
+      </c>
       <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
+      <c r="E7" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>121</v>
+      </c>
       <c r="G7" s="9" t="s">
         <v>55</v>
       </c>
@@ -1558,10 +1577,10 @@
         <v>96</v>
       </c>
       <c r="J7" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="K7" s="5" t="s">
         <v>119</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>120</v>
       </c>
       <c r="L7" s="5" t="s">
         <v>67</v>
@@ -1590,6 +1609,9 @@
       <c r="T7" s="12" t="s">
         <v>61</v>
       </c>
+      <c r="U7" s="5" t="s">
+        <v>123</v>
+      </c>
       <c r="V7" s="5" t="s">
         <v>42</v>
       </c>
@@ -1601,6 +1623,9 @@
       </c>
       <c r="AA7" s="5" t="s">
         <v>83</v>
+      </c>
+      <c r="AB7" s="5" t="s">
+        <v>124</v>
       </c>
       <c r="AC7" s="5" t="s">
         <v>88</v>
